--- a/график работы SearchMas.xlsx
+++ b/график работы SearchMas.xlsx
@@ -75,6 +75,7 @@
     </font>
     <font>
       <sz val="9"/>
+      <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -252,10 +253,10 @@
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.0855651955237017"/>
-          <c:y val="0.160110967997622"/>
-          <c:w val="0.883314472526091"/>
-          <c:h val="0.698107599326266"/>
+          <c:x val="0.0855678853226871"/>
+          <c:y val="0.160126833135157"/>
+          <c:w val="0.883247933104901"/>
+          <c:h val="0.697978596908442"/>
         </c:manualLayout>
       </c:layout>
       <c:scatterChart>
@@ -403,11 +404,11 @@
           </c:yVal>
           <c:smooth val="0"/>
         </c:ser>
-        <c:axId val="53224375"/>
-        <c:axId val="44549043"/>
+        <c:axId val="99306873"/>
+        <c:axId val="93494782"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="53224375"/>
+        <c:axId val="99306873"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -427,85 +428,12 @@
                 </a:pPr>
                 <a:r>
                   <a:rPr b="0" sz="900" strike="noStrike" u="none">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
                     <a:uFillTx/>
                     <a:latin typeface="Arial"/>
-                  </a:rPr>
-                  <a:t>Время (ms)</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln w="0">
-              <a:noFill/>
-            </a:ln>
-          </c:spPr>
-        </c:title>
-        <c:numFmt formatCode="General" sourceLinked="0"/>
-        <c:majorTickMark val="out"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:ln w="0">
-            <a:solidFill>
-              <a:srgbClr val="b3b3b3"/>
-            </a:solidFill>
-          </a:ln>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr b="0" sz="1000" strike="noStrike" u="none">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:uFillTx/>
-                <a:latin typeface="Arial"/>
-                <a:ea typeface="DejaVu Sans"/>
-              </a:defRPr>
-            </a:pPr>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="44549043"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
-      </c:valAx>
-      <c:valAx>
-        <c:axId val="44549043"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="0">
-              <a:solidFill>
-                <a:srgbClr val="b3b3b3"/>
-              </a:solidFill>
-            </a:ln>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr rot="-5400000"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr b="0" sz="1300" strike="noStrike" u="none">
-                    <a:uFillTx/>
-                    <a:latin typeface="Arial"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr b="0" sz="900" strike="noStrike" u="none">
-                    <a:uFillTx/>
-                    <a:latin typeface="Arial"/>
+                    <a:ea typeface="DejaVu Sans"/>
                   </a:rPr>
                   <a:t>Кол-во значений</a:t>
                 </a:r>
@@ -547,7 +475,88 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="53224375"/>
+        <c:crossAx val="93494782"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="93494782"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="0">
+              <a:solidFill>
+                <a:srgbClr val="b3b3b3"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1300" strike="noStrike" u="none">
+                    <a:uFillTx/>
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr b="0" sz="900" strike="noStrike" u="none">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:uFillTx/>
+                    <a:latin typeface="Arial"/>
+                    <a:ea typeface="DejaVu Sans"/>
+                  </a:rPr>
+                  <a:t>Время(ms)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln w="0">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="0"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln w="0">
+            <a:solidFill>
+              <a:srgbClr val="b3b3b3"/>
+            </a:solidFill>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="0" sz="1000" strike="noStrike" u="none">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:uFillTx/>
+                <a:latin typeface="Arial"/>
+                <a:ea typeface="DejaVu Sans"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="99306873"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -585,9 +594,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
-      <xdr:colOff>130680</xdr:colOff>
+      <xdr:colOff>129960</xdr:colOff>
       <xdr:row>22</xdr:row>
-      <xdr:rowOff>105120</xdr:rowOff>
+      <xdr:rowOff>104400</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -596,7 +605,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="1962000" y="47880"/>
-        <a:ext cx="11452320" cy="3633480"/>
+        <a:ext cx="11451600" cy="3632760"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
